--- a/Exp3_PTO_GRPO/eda/results/arms/preference/tables/gpt-4o-mini/preference.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/preference/tables/gpt-4o-mini/preference.xlsx
@@ -23616,13 +23616,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6592</v>
+        <v>0.6705</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8925999999999999</v>
+        <v>0.8945</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7385</v>
+        <v>0.7496</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -23684,13 +23684,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9842</v>
+        <v>0.984</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9323</v>
+        <v>0.9405</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0556</v>
+        <v>1.0462</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -23718,13 +23718,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.6695</v>
+        <v>0.6781</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9179</v>
+        <v>0.92</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7294</v>
+        <v>0.7371</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -23752,13 +23752,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.6387</v>
+        <v>0.6462</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8723</v>
+        <v>0.8781</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7323</v>
+        <v>0.736</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24525,46 +24525,46 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>6244</v>
+        <v>8856</v>
       </c>
       <c r="F17" t="n">
-        <v>286.8903</v>
+        <v>817.1188</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4206</v>
+        <v>2.4344</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.4779</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0113</v>
+        <v>0.0103</v>
       </c>
       <c r="J17" t="n">
-        <v>0.044</v>
+        <v>0.0716</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0016</v>
+        <v>0.0146</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0005</v>
+        <v>0.0013</v>
       </c>
     </row>
     <row r="18">
@@ -24582,34 +24582,34 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>4936</v>
+        <v>6244</v>
       </c>
       <c r="F18" t="n">
-        <v>318.4098</v>
+        <v>286.8903</v>
       </c>
       <c r="G18" t="n">
-        <v>2.8973</v>
+        <v>2.4206</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5999</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0133</v>
+        <v>0.0113</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0397</v>
+        <v>0.044</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0028</v>
+        <v>0.0026</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0018</v>
+        <v>0.0016</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="19">
@@ -24627,34 +24627,34 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>4947</v>
+        <v>4936</v>
       </c>
       <c r="F19" t="n">
-        <v>341.7787</v>
+        <v>318.4098</v>
       </c>
       <c r="G19" t="n">
-        <v>3.2824</v>
+        <v>2.8973</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5577</v>
+        <v>0.5999</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0122</v>
+        <v>0.0133</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0388</v>
+        <v>0.0397</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0027</v>
+        <v>0.0028</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0046</v>
+        <v>0.0018</v>
       </c>
       <c r="M19" t="n">
-        <v>0.001</v>
+        <v>0.0005999999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -24672,34 +24672,34 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>4283</v>
+        <v>4947</v>
       </c>
       <c r="F20" t="n">
-        <v>402.8735</v>
+        <v>341.7787</v>
       </c>
       <c r="G20" t="n">
-        <v>3.9719</v>
+        <v>3.2824</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5216</v>
+        <v>0.5577</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0146</v>
+        <v>0.0122</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0434</v>
+        <v>0.0388</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0031</v>
+        <v>0.0027</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0068</v>
+        <v>0.0046</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0013</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="21">
@@ -24717,31 +24717,31 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>3856</v>
+        <v>4283</v>
       </c>
       <c r="F21" t="n">
-        <v>547.3071</v>
+        <v>402.8735</v>
       </c>
       <c r="G21" t="n">
-        <v>5.0162</v>
+        <v>3.9719</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4878</v>
+        <v>0.5216</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0175</v>
+        <v>0.0146</v>
       </c>
       <c r="J21" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.0434</v>
       </c>
       <c r="K21" t="n">
-        <v>0.004</v>
+        <v>0.0031</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0062</v>
+        <v>0.0068</v>
       </c>
       <c r="M21" t="n">
         <v>0.0013</v>
@@ -24762,34 +24762,34 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>3795</v>
+        <v>3856</v>
       </c>
       <c r="F22" t="n">
-        <v>598.8274</v>
+        <v>547.3071</v>
       </c>
       <c r="G22" t="n">
-        <v>5.1044</v>
+        <v>5.0162</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5091</v>
+        <v>0.4878</v>
       </c>
       <c r="I22" t="n">
-        <v>0.018</v>
+        <v>0.0175</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1088</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0051</v>
+        <v>0.004</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0266</v>
+        <v>0.0062</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0026</v>
+        <v>0.0013</v>
       </c>
     </row>
     <row r="23">
@@ -24807,34 +24807,34 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>3194</v>
+        <v>3795</v>
       </c>
       <c r="F23" t="n">
-        <v>744.489</v>
+        <v>598.8274</v>
       </c>
       <c r="G23" t="n">
-        <v>5.0134</v>
+        <v>5.1044</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3278</v>
+        <v>0.5091</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0163</v>
+        <v>0.018</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1988</v>
+        <v>0.1088</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0071</v>
+        <v>0.0051</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0704</v>
+        <v>0.0266</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0045</v>
+        <v>0.0026</v>
       </c>
     </row>
     <row r="24">
@@ -24852,34 +24852,34 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>3023</v>
+        <v>3194</v>
       </c>
       <c r="F24" t="n">
-        <v>702.8475</v>
+        <v>744.489</v>
       </c>
       <c r="G24" t="n">
-        <v>5.4531</v>
+        <v>5.0134</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3414</v>
+        <v>0.3278</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0162</v>
+        <v>0.0163</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2603</v>
+        <v>0.1988</v>
       </c>
       <c r="K24" t="n">
-        <v>0.008</v>
+        <v>0.0071</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1105</v>
+        <v>0.0704</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0057</v>
+        <v>0.0045</v>
       </c>
     </row>
     <row r="25">
@@ -24897,34 +24897,34 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>2881</v>
+        <v>3023</v>
       </c>
       <c r="F25" t="n">
-        <v>822.6768</v>
+        <v>702.8475</v>
       </c>
       <c r="G25" t="n">
-        <v>4.8086</v>
+        <v>5.4531</v>
       </c>
       <c r="H25" t="n">
-        <v>0.336</v>
+        <v>0.3414</v>
       </c>
       <c r="I25" t="n">
-        <v>0.018</v>
+        <v>0.0162</v>
       </c>
       <c r="J25" t="n">
-        <v>0.353</v>
+        <v>0.2603</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0089</v>
+        <v>0.008</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1538</v>
+        <v>0.1105</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0067</v>
+        <v>0.0057</v>
       </c>
     </row>
     <row r="26">
@@ -24942,40 +24942,40 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>2237</v>
+        <v>2881</v>
       </c>
       <c r="F26" t="n">
-        <v>857.1498</v>
+        <v>822.6768</v>
       </c>
       <c r="G26" t="n">
-        <v>4.0816</v>
+        <v>4.8086</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2718</v>
+        <v>0.336</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0172</v>
+        <v>0.018</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5713</v>
+        <v>0.353</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0105</v>
+        <v>0.0089</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3178</v>
+        <v>0.1538</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0098</v>
+        <v>0.0067</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -24984,37 +24984,37 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>6634</v>
+        <v>2237</v>
       </c>
       <c r="F27" t="n">
-        <v>311.1577</v>
+        <v>857.1498</v>
       </c>
       <c r="G27" t="n">
-        <v>2.6631</v>
+        <v>4.0816</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6001</v>
+        <v>0.2718</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0103</v>
+        <v>0.0172</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0534</v>
+        <v>0.5713</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0028</v>
+        <v>0.0105</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0035</v>
+        <v>0.3178</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0007</v>
+        <v>0.0098</v>
       </c>
     </row>
     <row r="28">
@@ -25032,31 +25032,31 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>6215</v>
+        <v>6634</v>
       </c>
       <c r="F28" t="n">
-        <v>360.4904</v>
+        <v>311.1577</v>
       </c>
       <c r="G28" t="n">
-        <v>2.9099</v>
+        <v>2.6631</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5891</v>
+        <v>0.6001</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0113</v>
+        <v>0.0103</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0502</v>
+        <v>0.0534</v>
       </c>
       <c r="K28" t="n">
         <v>0.0028</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0029</v>
+        <v>0.0035</v>
       </c>
       <c r="M28" t="n">
         <v>0.0007</v>
@@ -25077,34 +25077,34 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>6139</v>
+        <v>6215</v>
       </c>
       <c r="F29" t="n">
-        <v>451.5216</v>
+        <v>360.4904</v>
       </c>
       <c r="G29" t="n">
-        <v>3.3366</v>
+        <v>2.9099</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5854</v>
+        <v>0.5891</v>
       </c>
       <c r="I29" t="n">
-        <v>0.012</v>
+        <v>0.0113</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0536</v>
+        <v>0.0502</v>
       </c>
       <c r="K29" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="L29" t="n">
         <v>0.0029</v>
       </c>
-      <c r="L29" t="n">
-        <v>0.0064</v>
-      </c>
       <c r="M29" t="n">
-        <v>0.001</v>
+        <v>0.0007</v>
       </c>
     </row>
     <row r="30">
@@ -25122,34 +25122,34 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>4501</v>
+        <v>6139</v>
       </c>
       <c r="F30" t="n">
-        <v>565.1822</v>
+        <v>451.5216</v>
       </c>
       <c r="G30" t="n">
-        <v>3.9678</v>
+        <v>3.3366</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5501</v>
+        <v>0.5854</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0152</v>
+        <v>0.012</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0655</v>
+        <v>0.0536</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0037</v>
+        <v>0.0029</v>
       </c>
       <c r="L30" t="n">
-        <v>0.014</v>
+        <v>0.0064</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0018</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="31">
@@ -25167,34 +25167,34 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>3132</v>
+        <v>4501</v>
       </c>
       <c r="F31" t="n">
-        <v>629.5639</v>
+        <v>565.1822</v>
       </c>
       <c r="G31" t="n">
-        <v>4.8893</v>
+        <v>3.9678</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5026</v>
+        <v>0.5501</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0177</v>
+        <v>0.0152</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0722</v>
+        <v>0.0655</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0046</v>
+        <v>0.0037</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0112</v>
+        <v>0.014</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0019</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="32">
@@ -25212,34 +25212,34 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>4536</v>
+        <v>3132</v>
       </c>
       <c r="F32" t="n">
-        <v>748.8682</v>
+        <v>629.5639</v>
       </c>
       <c r="G32" t="n">
-        <v>3.7919</v>
+        <v>4.8893</v>
       </c>
       <c r="H32" t="n">
-        <v>0.4634</v>
+        <v>0.5026</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0135</v>
+        <v>0.0177</v>
       </c>
       <c r="J32" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0722</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0039</v>
+        <v>0.0046</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0154</v>
+        <v>0.0112</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0018</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="33">
@@ -25257,34 +25257,34 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>5501</v>
+        <v>4536</v>
       </c>
       <c r="F33" t="n">
-        <v>834.7949</v>
+        <v>748.8682</v>
       </c>
       <c r="G33" t="n">
-        <v>3.113</v>
+        <v>3.7919</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5026</v>
+        <v>0.4634</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0157</v>
+        <v>0.0135</v>
       </c>
       <c r="J33" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0034</v>
+        <v>0.0039</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0165</v>
+        <v>0.0154</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0017</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="34">
@@ -25302,34 +25302,34 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E34" t="n">
-        <v>4517</v>
+        <v>5501</v>
       </c>
       <c r="F34" t="n">
-        <v>948.4625</v>
+        <v>834.7949</v>
       </c>
       <c r="G34" t="n">
-        <v>2.595</v>
+        <v>3.113</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2685</v>
+        <v>0.5026</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0102</v>
+        <v>0.0157</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0872</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0042</v>
+        <v>0.0034</v>
       </c>
       <c r="L34" t="n">
-        <v>0.0425</v>
+        <v>0.0165</v>
       </c>
       <c r="M34" t="n">
-        <v>0.003</v>
+        <v>0.0017</v>
       </c>
     </row>
     <row r="35">
@@ -25347,31 +25347,31 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E35" t="n">
-        <v>4825</v>
+        <v>4517</v>
       </c>
       <c r="F35" t="n">
-        <v>966.7542</v>
+        <v>948.4625</v>
       </c>
       <c r="G35" t="n">
-        <v>2.5652</v>
+        <v>2.595</v>
       </c>
       <c r="H35" t="n">
-        <v>0.308</v>
+        <v>0.2685</v>
       </c>
       <c r="I35" t="n">
         <v>0.0102</v>
       </c>
       <c r="J35" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0872</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0039</v>
+        <v>0.0042</v>
       </c>
       <c r="L35" t="n">
-        <v>0.0454</v>
+        <v>0.0425</v>
       </c>
       <c r="M35" t="n">
         <v>0.003</v>
@@ -25392,33 +25392,78 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
+        <v>9</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4825</v>
+      </c>
+      <c r="F36" t="n">
+        <v>966.7542</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.5652</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.07770000000000001</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.0454</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" t="n">
         <v>10</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E37" t="n">
         <v>4932</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F37" t="n">
         <v>1004.9017</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G37" t="n">
         <v>2.1629</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H37" t="n">
         <v>0.3228</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I37" t="n">
         <v>0.0103</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J37" t="n">
         <v>0.08699999999999999</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K37" t="n">
         <v>0.004</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L37" t="n">
         <v>0.0649</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M37" t="n">
         <v>0.0035</v>
       </c>
     </row>
@@ -25433,7 +25478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25931,31 +25976,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>949</v>
+        <v>1120</v>
       </c>
       <c r="E17" t="n">
-        <v>782</v>
+        <v>1107</v>
       </c>
       <c r="F17" t="n">
-        <v>0.824</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2735</v>
+        <v>0.3718</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2294</v>
+        <v>0.2882</v>
       </c>
     </row>
     <row r="18">
@@ -25970,22 +26015,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>772</v>
+        <v>949</v>
       </c>
       <c r="E18" t="n">
-        <v>618</v>
+        <v>782</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8005</v>
+        <v>0.824</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2502</v>
+        <v>0.2735</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2176</v>
+        <v>0.2294</v>
       </c>
     </row>
     <row r="19">
@@ -26000,22 +26045,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>787</v>
+        <v>772</v>
       </c>
       <c r="E19" t="n">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.8005</v>
       </c>
       <c r="G19" t="n">
-        <v>0.244</v>
+        <v>0.2502</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2059</v>
+        <v>0.2176</v>
       </c>
     </row>
     <row r="20">
@@ -26030,19 +26075,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>647</v>
+        <v>787</v>
       </c>
       <c r="E20" t="n">
-        <v>536</v>
+        <v>620</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8284</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2318</v>
+        <v>0.244</v>
       </c>
       <c r="H20" t="n">
         <v>0.2059</v>
@@ -26060,19 +26105,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>600</v>
+        <v>647</v>
       </c>
       <c r="E21" t="n">
-        <v>483</v>
+        <v>536</v>
       </c>
       <c r="F21" t="n">
-        <v>0.805</v>
+        <v>0.8284</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2367</v>
+        <v>0.2318</v>
       </c>
       <c r="H21" t="n">
         <v>0.2059</v>
@@ -26090,22 +26135,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="E22" t="n">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8037</v>
+        <v>0.805</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2253</v>
+        <v>0.2367</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2</v>
+        <v>0.2059</v>
       </c>
     </row>
     <row r="23">
@@ -26120,19 +26165,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>521</v>
+        <v>591</v>
       </c>
       <c r="E23" t="n">
-        <v>400</v>
+        <v>475</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7678</v>
+        <v>0.8037</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2202</v>
+        <v>0.2253</v>
       </c>
       <c r="H23" t="n">
         <v>0.2</v>
@@ -26150,22 +26195,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E24" t="n">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7331</v>
+        <v>0.7678</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1953</v>
+        <v>0.2202</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1765</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="25">
@@ -26180,22 +26225,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>446</v>
+        <v>517</v>
       </c>
       <c r="E25" t="n">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8094</v>
+        <v>0.7331</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2253</v>
+        <v>0.1953</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2059</v>
+        <v>0.1765</v>
       </c>
     </row>
     <row r="26">
@@ -26210,28 +26255,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>410</v>
+        <v>446</v>
       </c>
       <c r="E26" t="n">
-        <v>281</v>
+        <v>361</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6854</v>
+        <v>0.8094</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1958</v>
+        <v>0.2253</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1765</v>
+        <v>0.2059</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -26240,22 +26285,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>890</v>
+        <v>410</v>
       </c>
       <c r="E27" t="n">
-        <v>832</v>
+        <v>281</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9348</v>
+        <v>0.6854</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4242</v>
+        <v>0.1958</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3765</v>
+        <v>0.1765</v>
       </c>
     </row>
     <row r="28">
@@ -26270,22 +26315,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>837</v>
+        <v>890</v>
       </c>
       <c r="E28" t="n">
-        <v>778</v>
+        <v>832</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9295</v>
+        <v>0.9348</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4317</v>
+        <v>0.4242</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3882</v>
+        <v>0.3765</v>
       </c>
     </row>
     <row r="29">
@@ -26300,22 +26345,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>816</v>
+        <v>837</v>
       </c>
       <c r="E29" t="n">
-        <v>768</v>
+        <v>778</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9412</v>
+        <v>0.9295</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4447</v>
+        <v>0.4317</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3824</v>
+        <v>0.3882</v>
       </c>
     </row>
     <row r="30">
@@ -26330,22 +26375,22 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>613</v>
+        <v>816</v>
       </c>
       <c r="E30" t="n">
-        <v>563</v>
+        <v>768</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9184</v>
+        <v>0.9412</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3965</v>
+        <v>0.4447</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3353</v>
+        <v>0.3824</v>
       </c>
     </row>
     <row r="31">
@@ -26360,22 +26405,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>468</v>
+        <v>613</v>
       </c>
       <c r="E31" t="n">
-        <v>432</v>
+        <v>563</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9231</v>
+        <v>0.9184</v>
       </c>
       <c r="G31" t="n">
-        <v>0.381</v>
+        <v>0.3965</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3294</v>
+        <v>0.3353</v>
       </c>
     </row>
     <row r="32">
@@ -26390,22 +26435,22 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>663</v>
+        <v>468</v>
       </c>
       <c r="E32" t="n">
-        <v>568</v>
+        <v>432</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8567</v>
+        <v>0.9231</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3324</v>
+        <v>0.381</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2882</v>
+        <v>0.3294</v>
       </c>
     </row>
     <row r="33">
@@ -26420,22 +26465,22 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>807</v>
+        <v>663</v>
       </c>
       <c r="E33" t="n">
-        <v>689</v>
+        <v>568</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8538</v>
+        <v>0.8567</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3318</v>
+        <v>0.3324</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2941</v>
+        <v>0.2882</v>
       </c>
     </row>
     <row r="34">
@@ -26450,22 +26495,22 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>767</v>
+        <v>807</v>
       </c>
       <c r="E34" t="n">
-        <v>565</v>
+        <v>689</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7366</v>
+        <v>0.8538</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2731</v>
+        <v>0.3318</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1882</v>
+        <v>0.2941</v>
       </c>
     </row>
     <row r="35">
@@ -26480,22 +26525,22 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="E35" t="n">
-        <v>604</v>
+        <v>565</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7937</v>
+        <v>0.7366</v>
       </c>
       <c r="G35" t="n">
-        <v>0.302</v>
+        <v>0.2731</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2176</v>
+        <v>0.1882</v>
       </c>
     </row>
     <row r="36">
@@ -26510,21 +26555,51 @@
         </is>
       </c>
       <c r="C36" t="n">
+        <v>9</v>
+      </c>
+      <c r="D36" t="n">
+        <v>761</v>
+      </c>
+      <c r="E36" t="n">
+        <v>604</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.7937</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.2176</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
         <v>10</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D37" t="n">
         <v>926</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E37" t="n">
         <v>617</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F37" t="n">
         <v>0.6663</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G37" t="n">
         <v>0.2336</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H37" t="n">
         <v>0.1529</v>
       </c>
     </row>
@@ -26794,19 +26869,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>1.459</v>
+        <v>4.912</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>While small changes can certainly help momentum and confidence, it's also important to explore other options that might better suit you. Sometimes, sticking to existing habits or steps towards bigger goals can be easier and more achievable. For example, instead of trying to force yourself to make radical changes to you…</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Sure, you can take small steps to make changes that are manageable. One thing that you could focus on is incorporating healthier options into your diet by trying out new fruits and vegetables, sources of whole grains and lean proteins, and low-fat sources of dairy. Having these resources in your pantry or refrigerator …</t>
+          <t>Awesome! It’s rewarding to hear that you’re feeling confident, driven, and ready to take the next steps on your health journey. As we finish this session, I’m encouraged by your commitment and enthusiasm to stay on track. I hope you noticed that I personalized the advice based on what works best for you—we all need to …</t>
         </is>
       </c>
     </row>
@@ -26817,19 +26887,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>1.435</v>
+        <v>1.476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>I see what you're saying, and I get it that it's challenging to come back to the same topic again and again. The point is not to come up with a set of strategies or a plan that's going to work once and then put an end to it. The goal is for you to find a way to support yourself so you feel the same level of engagement …</t>
+          <t>That's a valid concern. If you want to reduce cravings directly and manage resistant cravings, there are several different options that could help. First, there are nicotine replacement systems that can provide a gradual reduction in your nicotine exposure. You can find products such as gum, patch, lozenge, or nasal sp…</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fair to say that's not ideal. It can be helpful to be able to give suggestions that help someone feel more supported, but a specific plan isn't always realistic or achievable. Let's look at some considerations:</t>
+          <t>Yeah, using nicotine replacement options may be a common recommendation for people who struggle with cravings. However, it's important to remember that nicotine isn't the only thing that can trigger a craving and help with withdrawal symptoms. It's also about identifying the triggers and working on changes that can red…</t>
         </is>
       </c>
     </row>
@@ -26840,19 +26910,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>1.388</v>
+        <v>1.465</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>You're right, changing everything at once isn't always necessary. Maybe you can start small and work your way up. Start by eating a handful of colorful snacks or fruits everyday. That way, you won't have to deprive yourself of anything, but you'll start to see small positive changes in your overall health. Over time, y…</t>
+          <t>It sounds like you're looking for a process that guides you through that thinking as well as the actions you can focus on during those moments. Here's one approach that you could try: First, recognize that recognizing your urges can be helpful. It gives you a chance to pause before taking action and makes it easier to …</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Okay, I hear what you're saying. The thing is, you have to figure things out for yourself. Maybe it's something that has more practical support, like joining a gym or making healthy food available at home. Whatever you choose, the important thing is that it feels good and works for you.</t>
+          <t>I hear what you're saying, and I think your questions are a great place to start. It might be helpful to think of your coping skills as a toolbox or a set of temporary, short-term solutions that you can select from when pminds hit you. What are some things you do that might help you feel on top of your emotions or at e…</t>
         </is>
       </c>
     </row>
@@ -29428,7 +29498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30226,49 +30296,49 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>782</v>
+        <v>1107</v>
       </c>
       <c r="F17" t="n">
-        <v>1564</v>
+        <v>8809</v>
       </c>
       <c r="G17" t="n">
-        <v>-7.9258</v>
+        <v>10.345</v>
       </c>
       <c r="H17" t="n">
-        <v>7.4241</v>
+        <v>5.3556</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0767</v>
+        <v>0.0563</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0428</v>
+        <v>0.0241</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0077</v>
+        <v>-0.0004</v>
       </c>
       <c r="L17" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0066</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0013</v>
+        <v>0.006</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0022</v>
+        <v>0.0032</v>
       </c>
     </row>
     <row r="18">
@@ -30286,37 +30356,37 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>618</v>
+        <v>782</v>
       </c>
       <c r="F18" t="n">
-        <v>1236</v>
+        <v>1564</v>
       </c>
       <c r="G18" t="n">
-        <v>3.6715</v>
+        <v>-7.9258</v>
       </c>
       <c r="H18" t="n">
-        <v>9.5037</v>
+        <v>7.4241</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0016</v>
+        <v>-0.0767</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0474</v>
+        <v>0.0428</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0016</v>
+        <v>0.0077</v>
       </c>
       <c r="L18" t="n">
-        <v>0.012</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0049</v>
+        <v>0.0013</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0028</v>
+        <v>0.0022</v>
       </c>
     </row>
     <row r="19">
@@ -30334,37 +30404,37 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="F19" t="n">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="G19" t="n">
-        <v>8.2484</v>
+        <v>3.6715</v>
       </c>
       <c r="H19" t="n">
-        <v>11.1533</v>
+        <v>9.5037</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0065</v>
+        <v>-0.0016</v>
       </c>
       <c r="J19" t="n">
-        <v>0.041</v>
+        <v>0.0474</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-0.0016</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0116</v>
+        <v>0.012</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0016</v>
+        <v>0.0049</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0043</v>
+        <v>0.0028</v>
       </c>
     </row>
     <row r="20">
@@ -30382,37 +30452,37 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>536</v>
+        <v>620</v>
       </c>
       <c r="F20" t="n">
-        <v>1072</v>
+        <v>1240</v>
       </c>
       <c r="G20" t="n">
-        <v>-21.7295</v>
+        <v>8.2484</v>
       </c>
       <c r="H20" t="n">
-        <v>12.8167</v>
+        <v>11.1533</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0728</v>
+        <v>0.0065</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0518</v>
+        <v>0.041</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0168</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0125</v>
+        <v>0.0116</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0075</v>
+        <v>0.0016</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0046</v>
+        <v>0.0043</v>
       </c>
     </row>
     <row r="21">
@@ -30430,34 +30500,34 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>483</v>
+        <v>536</v>
       </c>
       <c r="F21" t="n">
-        <v>966</v>
+        <v>1072</v>
       </c>
       <c r="G21" t="n">
-        <v>6.6232</v>
+        <v>-21.7295</v>
       </c>
       <c r="H21" t="n">
-        <v>15.7636</v>
+        <v>12.8167</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.029</v>
+        <v>-0.0728</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0731</v>
+        <v>0.0518</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0083</v>
+        <v>0.0168</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0163</v>
+        <v>0.0125</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0021</v>
+        <v>-0.0075</v>
       </c>
       <c r="N21" t="n">
         <v>0.0046</v>
@@ -30478,37 +30548,37 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="F22" t="n">
-        <v>950</v>
+        <v>966</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.2674</v>
+        <v>6.6232</v>
       </c>
       <c r="H22" t="n">
-        <v>15.3491</v>
+        <v>15.7636</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1895</v>
+        <v>-0.029</v>
       </c>
       <c r="J22" t="n">
-        <v>0.073</v>
+        <v>0.0731</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0105</v>
+        <v>0.0083</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0203</v>
+        <v>0.0163</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0105</v>
+        <v>0.0021</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0101</v>
+        <v>0.0046</v>
       </c>
     </row>
     <row r="23">
@@ -30526,37 +30596,37 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>400</v>
+        <v>475</v>
       </c>
       <c r="F23" t="n">
-        <v>800</v>
+        <v>950</v>
       </c>
       <c r="G23" t="n">
-        <v>-11.1</v>
+        <v>-6.2674</v>
       </c>
       <c r="H23" t="n">
-        <v>15.0167</v>
+        <v>15.3491</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0425</v>
+        <v>-0.1895</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0608</v>
+        <v>0.073</v>
       </c>
       <c r="K23" t="n">
-        <v>0.05</v>
+        <v>0.0105</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0254</v>
+        <v>0.0203</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0625</v>
+        <v>-0.0105</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0172</v>
+        <v>0.0101</v>
       </c>
     </row>
     <row r="24">
@@ -30574,37 +30644,37 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="F24" t="n">
-        <v>758</v>
+        <v>800</v>
       </c>
       <c r="G24" t="n">
-        <v>2.3799</v>
+        <v>-11.1</v>
       </c>
       <c r="H24" t="n">
-        <v>15.1092</v>
+        <v>15.0167</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0132</v>
+        <v>-0.0425</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0667</v>
+        <v>0.0608</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1029</v>
+        <v>0.05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0286</v>
+        <v>0.0254</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0343</v>
+        <v>0.0625</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0209</v>
+        <v>0.0172</v>
       </c>
     </row>
     <row r="25">
@@ -30622,37 +30692,37 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="F25" t="n">
-        <v>722</v>
+        <v>758</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.1247</v>
+        <v>2.3799</v>
       </c>
       <c r="H25" t="n">
-        <v>16.6026</v>
+        <v>15.1092</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.133</v>
+        <v>0.0132</v>
       </c>
       <c r="J25" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.0667</v>
       </c>
       <c r="K25" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.1029</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0316</v>
+        <v>0.0286</v>
       </c>
       <c r="M25" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0343</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0253</v>
+        <v>0.0209</v>
       </c>
     </row>
     <row r="26">
@@ -30670,43 +30740,43 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>281</v>
+        <v>361</v>
       </c>
       <c r="F26" t="n">
-        <v>562</v>
+        <v>722</v>
       </c>
       <c r="G26" t="n">
-        <v>23.3915</v>
+        <v>-3.1247</v>
       </c>
       <c r="H26" t="n">
-        <v>14.639</v>
+        <v>16.6026</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0107</v>
+        <v>-0.133</v>
       </c>
       <c r="J26" t="n">
-        <v>0.052</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0391</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0382</v>
+        <v>0.0316</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0391</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>0.0332</v>
+        <v>0.0253</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -30715,40 +30785,40 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>832</v>
+        <v>281</v>
       </c>
       <c r="F27" t="n">
-        <v>1664</v>
+        <v>562</v>
       </c>
       <c r="G27" t="n">
-        <v>49.4796</v>
+        <v>23.3915</v>
       </c>
       <c r="H27" t="n">
-        <v>7.5976</v>
+        <v>14.639</v>
       </c>
       <c r="I27" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.0107</v>
       </c>
       <c r="J27" t="n">
-        <v>0.035</v>
+        <v>0.052</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0216</v>
+        <v>0.0391</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0106</v>
+        <v>0.0382</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0012</v>
+        <v>-0.0391</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0032</v>
+        <v>0.0332</v>
       </c>
     </row>
     <row r="28">
@@ -30766,34 +30836,34 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>778</v>
+        <v>832</v>
       </c>
       <c r="F28" t="n">
-        <v>1556</v>
+        <v>1664</v>
       </c>
       <c r="G28" t="n">
-        <v>45.1465</v>
+        <v>49.4796</v>
       </c>
       <c r="H28" t="n">
-        <v>8.643700000000001</v>
+        <v>7.5976</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0039</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0397</v>
+        <v>0.035</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0129</v>
+        <v>0.0216</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0103</v>
+        <v>0.0106</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>0.0012</v>
       </c>
       <c r="N28" t="n">
         <v>0.0032</v>
@@ -30814,37 +30884,37 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>768</v>
+        <v>778</v>
       </c>
       <c r="F29" t="n">
-        <v>1536</v>
+        <v>1556</v>
       </c>
       <c r="G29" t="n">
-        <v>58.8685</v>
+        <v>45.1465</v>
       </c>
       <c r="H29" t="n">
-        <v>9.037000000000001</v>
+        <v>8.643700000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>0.099</v>
+        <v>-0.0039</v>
       </c>
       <c r="J29" t="n">
-        <v>0.042</v>
+        <v>0.0397</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0078</v>
+        <v>0.0129</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0101</v>
+        <v>0.0103</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0078</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0.0037</v>
+        <v>0.0032</v>
       </c>
     </row>
     <row r="30">
@@ -30862,37 +30932,37 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>563</v>
+        <v>768</v>
       </c>
       <c r="F30" t="n">
-        <v>1126</v>
+        <v>1536</v>
       </c>
       <c r="G30" t="n">
-        <v>29.0853</v>
+        <v>58.8685</v>
       </c>
       <c r="H30" t="n">
-        <v>11.4516</v>
+        <v>9.037000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0551</v>
+        <v>0.099</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0489</v>
+        <v>0.042</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0231</v>
+        <v>0.0078</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0145</v>
+        <v>0.0101</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0053</v>
+        <v>0.0078</v>
       </c>
       <c r="N30" t="n">
-        <v>0.0059</v>
+        <v>0.0037</v>
       </c>
     </row>
     <row r="31">
@@ -30910,37 +30980,37 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>432</v>
+        <v>563</v>
       </c>
       <c r="F31" t="n">
-        <v>864</v>
+        <v>1126</v>
       </c>
       <c r="G31" t="n">
-        <v>32.4491</v>
+        <v>29.0853</v>
       </c>
       <c r="H31" t="n">
-        <v>13.9224</v>
+        <v>11.4516</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1019</v>
+        <v>-0.0551</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0665</v>
+        <v>0.0489</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0208</v>
+        <v>0.0231</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0172</v>
+        <v>0.0145</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>0.0053</v>
       </c>
       <c r="N31" t="n">
-        <v>0.0073</v>
+        <v>0.0059</v>
       </c>
     </row>
     <row r="32">
@@ -30958,37 +31028,37 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>568</v>
+        <v>432</v>
       </c>
       <c r="F32" t="n">
-        <v>1136</v>
+        <v>864</v>
       </c>
       <c r="G32" t="n">
-        <v>28.3011</v>
+        <v>32.4491</v>
       </c>
       <c r="H32" t="n">
-        <v>10.9304</v>
+        <v>13.9224</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0757</v>
+        <v>-0.1019</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0393</v>
+        <v>0.0665</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.0211</v>
+        <v>0.0208</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0155</v>
+        <v>0.0172</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0035</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0.0075</v>
+        <v>0.0073</v>
       </c>
     </row>
     <row r="33">
@@ -31006,37 +31076,37 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>689</v>
+        <v>568</v>
       </c>
       <c r="F33" t="n">
-        <v>1378</v>
+        <v>1136</v>
       </c>
       <c r="G33" t="n">
-        <v>53.7881</v>
+        <v>28.3011</v>
       </c>
       <c r="H33" t="n">
-        <v>9.319100000000001</v>
+        <v>10.9304</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0421</v>
+        <v>0.0757</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0502</v>
+        <v>0.0393</v>
       </c>
       <c r="K33" t="n">
-        <v>0.016</v>
+        <v>-0.0211</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0134</v>
+        <v>0.0155</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.0044</v>
+        <v>0.0035</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0063</v>
+        <v>0.0075</v>
       </c>
     </row>
     <row r="34">
@@ -31054,37 +31124,37 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E34" t="n">
-        <v>565</v>
+        <v>689</v>
       </c>
       <c r="F34" t="n">
-        <v>1130</v>
+        <v>1378</v>
       </c>
       <c r="G34" t="n">
-        <v>20</v>
+        <v>53.7881</v>
       </c>
       <c r="H34" t="n">
-        <v>8.755800000000001</v>
+        <v>9.319100000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0389</v>
+        <v>-0.0421</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0345</v>
+        <v>0.0502</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.0053</v>
+        <v>0.016</v>
       </c>
       <c r="L34" t="n">
-        <v>0.0165</v>
+        <v>0.0134</v>
       </c>
       <c r="M34" t="n">
-        <v>0.0248</v>
+        <v>-0.0044</v>
       </c>
       <c r="N34" t="n">
-        <v>0.0122</v>
+        <v>0.0063</v>
       </c>
     </row>
     <row r="35">
@@ -31102,37 +31172,37 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E35" t="n">
-        <v>604</v>
+        <v>565</v>
       </c>
       <c r="F35" t="n">
-        <v>1208</v>
+        <v>1130</v>
       </c>
       <c r="G35" t="n">
-        <v>26.7036</v>
+        <v>20</v>
       </c>
       <c r="H35" t="n">
-        <v>8.1838</v>
+        <v>8.755800000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0232</v>
+        <v>0.0389</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0351</v>
+        <v>0.0345</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.0053</v>
       </c>
       <c r="L35" t="n">
-        <v>0.0161</v>
+        <v>0.0165</v>
       </c>
       <c r="M35" t="n">
-        <v>0.0033</v>
+        <v>0.0248</v>
       </c>
       <c r="N35" t="n">
-        <v>0.0112</v>
+        <v>0.0122</v>
       </c>
     </row>
     <row r="36">
@@ -31150,36 +31220,84 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
+        <v>9</v>
+      </c>
+      <c r="E36" t="n">
+        <v>604</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1208</v>
+      </c>
+      <c r="G36" t="n">
+        <v>26.7036</v>
+      </c>
+      <c r="H36" t="n">
+        <v>8.1838</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-0.009900000000000001</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.0112</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" t="n">
         <v>10</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E37" t="n">
         <v>617</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F37" t="n">
         <v>1234</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G37" t="n">
         <v>7.0162</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H37" t="n">
         <v>7.3362</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I37" t="n">
         <v>0.047</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J37" t="n">
         <v>0.0386</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K37" t="n">
         <v>-0.0227</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L37" t="n">
         <v>0.0162</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M37" t="n">
         <v>-0.0016</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N37" t="n">
         <v>0.0142</v>
       </c>
     </row>
@@ -31194,7 +31312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31742,34 +31860,34 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
         <v>400</v>
       </c>
       <c r="E17" t="n">
-        <v>800</v>
+        <v>3183</v>
       </c>
       <c r="F17" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0655</v>
+        <v>0.0612</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5225</v>
+        <v>0.5975</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1882</v>
+        <v>0.5341</v>
       </c>
     </row>
     <row r="18">
@@ -31784,7 +31902,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>400</v>
@@ -31793,16 +31911,16 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>0.665</v>
+        <v>0.73</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0614</v>
+        <v>0.0655</v>
       </c>
       <c r="H18" t="n">
-        <v>0.505</v>
+        <v>0.5225</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1467</v>
+        <v>0.1882</v>
       </c>
     </row>
     <row r="19">
@@ -31817,7 +31935,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
         <v>400</v>
@@ -31826,16 +31944,16 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6575</v>
+        <v>0.665</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0532</v>
+        <v>0.0614</v>
       </c>
       <c r="H19" t="n">
-        <v>0.465</v>
+        <v>0.505</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1547</v>
+        <v>0.1467</v>
       </c>
     </row>
     <row r="20">
@@ -31850,7 +31968,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
         <v>400</v>
@@ -31859,16 +31977,16 @@
         <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>0.655</v>
+        <v>0.6575</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0551</v>
+        <v>0.0532</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4975</v>
+        <v>0.465</v>
       </c>
       <c r="I20" t="n">
-        <v>0.022</v>
+        <v>-0.1547</v>
       </c>
     </row>
     <row r="21">
@@ -31883,7 +32001,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
         <v>400</v>
@@ -31892,16 +32010,16 @@
         <v>800</v>
       </c>
       <c r="F21" t="n">
-        <v>0.675</v>
+        <v>0.655</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0558</v>
+        <v>0.0551</v>
       </c>
       <c r="H21" t="n">
-        <v>0.525</v>
+        <v>0.4975</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1005</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="22">
@@ -31916,7 +32034,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
         <v>400</v>
@@ -31925,16 +32043,16 @@
         <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7025</v>
+        <v>0.675</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0602</v>
+        <v>0.0558</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5375</v>
+        <v>0.525</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1882</v>
+        <v>0.1005</v>
       </c>
     </row>
     <row r="23">
@@ -31949,7 +32067,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
         <v>400</v>
@@ -31958,16 +32076,16 @@
         <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6825</v>
+        <v>0.7025</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0513</v>
+        <v>0.0602</v>
       </c>
       <c r="H23" t="n">
-        <v>0.54</v>
+        <v>0.5375</v>
       </c>
       <c r="I23" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.1882</v>
       </c>
     </row>
     <row r="24">
@@ -31982,25 +32100,25 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="E24" t="n">
-        <v>758</v>
+        <v>800</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6623</v>
+        <v>0.6825</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0629</v>
+        <v>0.0513</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5461</v>
+        <v>0.54</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1997</v>
+        <v>0.08409999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -32015,25 +32133,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="E25" t="n">
-        <v>722</v>
+        <v>758</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7175</v>
+        <v>0.6623</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0594</v>
+        <v>0.0629</v>
       </c>
       <c r="H25" t="n">
-        <v>0.543</v>
+        <v>0.5461</v>
       </c>
       <c r="I25" t="n">
-        <v>0.196</v>
+        <v>0.1997</v>
       </c>
     </row>
     <row r="26">
@@ -32048,31 +32166,31 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>281</v>
+        <v>361</v>
       </c>
       <c r="E26" t="n">
-        <v>562</v>
+        <v>722</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7082000000000001</v>
+        <v>0.7175</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0624</v>
+        <v>0.0594</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5908</v>
+        <v>0.543</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3203</v>
+        <v>0.196</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -32081,25 +32199,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>400</v>
+        <v>281</v>
       </c>
       <c r="E27" t="n">
-        <v>800</v>
+        <v>562</v>
       </c>
       <c r="F27" t="n">
-        <v>0.665</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0992</v>
+        <v>0.0624</v>
       </c>
       <c r="H27" t="n">
-        <v>0.615</v>
+        <v>0.5908</v>
       </c>
       <c r="I27" t="n">
-        <v>0.537</v>
+        <v>0.3203</v>
       </c>
     </row>
     <row r="28">
@@ -32114,7 +32232,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
         <v>400</v>
@@ -32123,16 +32241,16 @@
         <v>800</v>
       </c>
       <c r="F28" t="n">
-        <v>0.64</v>
+        <v>0.665</v>
       </c>
       <c r="G28" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0992</v>
       </c>
       <c r="H28" t="n">
-        <v>0.575</v>
+        <v>0.615</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4601</v>
+        <v>0.537</v>
       </c>
     </row>
     <row r="29">
@@ -32147,7 +32265,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
         <v>400</v>
@@ -32156,16 +32274,16 @@
         <v>800</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6925</v>
+        <v>0.64</v>
       </c>
       <c r="G29" t="n">
-        <v>0.081</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>0.59</v>
+        <v>0.575</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3982</v>
+        <v>0.4601</v>
       </c>
     </row>
     <row r="30">
@@ -32180,7 +32298,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
         <v>400</v>
@@ -32189,16 +32307,16 @@
         <v>800</v>
       </c>
       <c r="F30" t="n">
-        <v>0.625</v>
+        <v>0.6925</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0635</v>
+        <v>0.081</v>
       </c>
       <c r="H30" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3055</v>
+        <v>0.3982</v>
       </c>
     </row>
     <row r="31">
@@ -32213,7 +32331,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
         <v>400</v>
@@ -32222,16 +32340,16 @@
         <v>800</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6775</v>
+        <v>0.625</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0593</v>
+        <v>0.0635</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5125</v>
+        <v>0.58</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0752</v>
+        <v>0.3055</v>
       </c>
     </row>
     <row r="32">
@@ -32246,7 +32364,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
         <v>400</v>
@@ -32255,16 +32373,16 @@
         <v>800</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6525</v>
+        <v>0.6775</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0524</v>
+        <v>0.0593</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5275</v>
+        <v>0.5125</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2614</v>
+        <v>0.0752</v>
       </c>
     </row>
     <row r="33">
@@ -32279,7 +32397,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D33" t="n">
         <v>400</v>
@@ -32288,16 +32406,16 @@
         <v>800</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6725</v>
+        <v>0.6525</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0588</v>
+        <v>0.0524</v>
       </c>
       <c r="H33" t="n">
-        <v>0.59</v>
+        <v>0.5275</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3495</v>
+        <v>0.2614</v>
       </c>
     </row>
     <row r="34">
@@ -32312,7 +32430,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D34" t="n">
         <v>400</v>
@@ -32321,16 +32439,16 @@
         <v>800</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6375</v>
+        <v>0.6725</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0459</v>
+        <v>0.0588</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5125</v>
+        <v>0.59</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0566</v>
+        <v>0.3495</v>
       </c>
     </row>
     <row r="35">
@@ -32345,7 +32463,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" t="n">
         <v>400</v>
@@ -32354,16 +32472,16 @@
         <v>800</v>
       </c>
       <c r="F35" t="n">
-        <v>0.665</v>
+        <v>0.6375</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0537</v>
+        <v>0.0459</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5575</v>
+        <v>0.5125</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3035</v>
+        <v>0.0566</v>
       </c>
     </row>
     <row r="36">
@@ -32378,7 +32496,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D36" t="n">
         <v>400</v>
@@ -32387,15 +32505,48 @@
         <v>800</v>
       </c>
       <c r="F36" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.5575</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.3035</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>10</v>
+      </c>
+      <c r="D37" t="n">
+        <v>400</v>
+      </c>
+      <c r="E37" t="n">
+        <v>800</v>
+      </c>
+      <c r="F37" t="n">
         <v>0.675</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G37" t="n">
         <v>0.0434</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H37" t="n">
         <v>0.505</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I37" t="n">
         <v>0.0111</v>
       </c>
     </row>
@@ -32505,25 +32656,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>2000</v>
+        <v>2400</v>
       </c>
       <c r="E3" t="n">
-        <v>15907</v>
+        <v>19090</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6165</v>
+        <v>0.6088</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0818</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.609</v>
+        <v>0.6021</v>
       </c>
       <c r="I3" t="n">
-        <v>0.912</v>
+        <v>0.9198</v>
       </c>
     </row>
     <row r="4">
@@ -32645,13 +32796,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8036</v>
+        <v>0.7983</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9538</v>
+        <v>0.9559</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8425</v>
+        <v>0.8352000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -32708,13 +32859,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1249</v>
+        <v>0.1109</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8445</v>
+        <v>0.8464</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1479</v>
+        <v>0.1311</v>
       </c>
     </row>
     <row r="6">
@@ -32729,13 +32880,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6592</v>
+        <v>0.6705</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8925999999999999</v>
+        <v>0.8945</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7385</v>
+        <v>0.7496</v>
       </c>
     </row>
     <row r="7">
